--- a/data_u1/reporting_bias_table_2025.08.15.xlsx
+++ b/data_u1/reporting_bias_table_2025.08.15.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BA705E-C9FD-CD41-960D-20FE3DCB4D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E914189-76F1-3849-9565-C458DAD0D674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{AFB5D0D2-F574-A541-B966-F5F755AA74BF}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="18000" xr2:uid="{AFB5D0D2-F574-A541-B966-F5F755AA74BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -3739,7 +3739,7 @@
         <v>77</v>
       </c>
       <c r="F18" s="23">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>29</v>
